--- a/Ozrit HR data/ozrit/Admin/Admin payment Details/Assets and Liabilities (Monthly report).xlsx
+++ b/Ozrit HR data/ozrit/Admin/Admin payment Details/Assets and Liabilities (Monthly report).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\Admin\Admin payment Details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954B2ED8-02A3-410E-AFC4-C8DD23698AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F394B861-328E-4182-A627-B26DA971A648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="August" sheetId="6" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="May" sheetId="2" r:id="rId4"/>
     <sheet name="April " sheetId="3" r:id="rId5"/>
     <sheet name="March " sheetId="4" r:id="rId6"/>
+    <sheet name="March to October " sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="214">
   <si>
     <t>Liabilities</t>
   </si>
@@ -597,19 +598,113 @@
   <si>
     <t xml:space="preserve">Ridev mail renewal </t>
   </si>
+  <si>
+    <t xml:space="preserve">Month </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">March </t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 setups systems </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR </t>
+  </si>
+  <si>
+    <t>Rows</t>
+  </si>
+  <si>
+    <t>1st Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd Row </t>
+  </si>
+  <si>
+    <t>android</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>3rd Row</t>
+  </si>
+  <si>
+    <t>4th Row</t>
+  </si>
+  <si>
+    <t>5th Row</t>
+  </si>
+  <si>
+    <t>6th Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7th Row </t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>Developers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server &amp; management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cabins </t>
+  </si>
+  <si>
+    <t>no.of setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor seater </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -845,8 +940,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF4E5E6A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -922,6 +1045,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1231,451 +1365,502 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="22" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="23" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="24" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="29" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="30" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="31" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="26" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="34" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="34" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="35" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="36" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="37" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="37" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="38" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="19" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="32" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="33" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="34" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="35" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="6" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="31" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="36" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="37" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{25FF4A7F-CC48-455E-A2C8-95E75ABD8BED}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1900,11 +2085,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="197"/>
-      <c r="B1" s="198" t="s">
+      <c r="A1" s="165"/>
+      <c r="B1" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="199" t="s">
+      <c r="C1" s="167" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1"/>
@@ -1917,13 +2102,13 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="200" t="s">
+      <c r="B2" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="200"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="11"/>
       <c r="E2" s="28"/>
       <c r="F2" s="13" t="s">
@@ -1932,11 +2117,11 @@
       <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="201"/>
-      <c r="B3" s="200" t="s">
+      <c r="A3" s="189"/>
+      <c r="B3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="200"/>
+      <c r="C3" s="168"/>
       <c r="D3" s="11"/>
       <c r="E3" s="28"/>
       <c r="F3" s="13" t="s">
@@ -1945,37 +2130,37 @@
       <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="200" t="s">
+      <c r="A4" s="189"/>
+      <c r="B4" s="168" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="200"/>
+      <c r="C4" s="168"/>
       <c r="D4" s="11"/>
       <c r="E4" s="28"/>
       <c r="F4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="205"/>
+      <c r="G4" s="171"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="201"/>
-      <c r="B5" s="200" t="s">
+      <c r="A5" s="189"/>
+      <c r="B5" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="215"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="11"/>
       <c r="E5" s="28"/>
       <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="205"/>
+      <c r="G5" s="171"/>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="201"/>
-      <c r="B6" s="200" t="s">
+      <c r="A6" s="189"/>
+      <c r="B6" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="216">
+      <c r="C6" s="182">
         <v>5300</v>
       </c>
       <c r="D6" s="11"/>
@@ -1983,14 +2168,14 @@
       <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="205"/>
+      <c r="G6" s="171"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="201"/>
-      <c r="B7" s="200" t="s">
+      <c r="A7" s="189"/>
+      <c r="B7" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="217">
+      <c r="C7" s="183">
         <v>15040.53</v>
       </c>
       <c r="D7" s="11"/>
@@ -1998,14 +2183,14 @@
       <c r="F7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="206"/>
+      <c r="G7" s="172"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="201"/>
-      <c r="B8" s="200" t="s">
+      <c r="A8" s="189"/>
+      <c r="B8" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="218">
+      <c r="C8" s="184">
         <v>13348</v>
       </c>
       <c r="D8" s="11"/>
@@ -2013,79 +2198,79 @@
       <c r="F8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="207"/>
+      <c r="G8" s="173"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="201"/>
-      <c r="B9" s="200" t="s">
+      <c r="A9" s="189"/>
+      <c r="B9" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="215"/>
+      <c r="C9" s="181"/>
       <c r="D9" s="11"/>
       <c r="E9" s="28"/>
       <c r="F9" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="207"/>
+      <c r="G9" s="173"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="201"/>
-      <c r="B10" s="200" t="s">
+      <c r="A10" s="189"/>
+      <c r="B10" s="168" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="215"/>
+      <c r="C10" s="181"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="186" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="184">
+      <c r="G10" s="155">
         <v>35061.910000000003</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="201"/>
-      <c r="B11" s="200" t="s">
+      <c r="A11" s="189"/>
+      <c r="B11" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="215"/>
+      <c r="C11" s="181"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="124"/>
+      <c r="E11" s="187"/>
       <c r="F11" s="27"/>
-      <c r="G11" s="205"/>
+      <c r="G11" s="171"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="201"/>
-      <c r="B12" s="200" t="s">
+      <c r="A12" s="189"/>
+      <c r="B12" s="168" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="215"/>
+      <c r="C12" s="181"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="125"/>
+      <c r="E12" s="188"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="205"/>
+      <c r="G12" s="171"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="201"/>
-      <c r="B13" s="200" t="s">
+      <c r="A13" s="189"/>
+      <c r="B13" s="168" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="215"/>
+      <c r="C13" s="181"/>
       <c r="D13" s="11"/>
       <c r="E13" s="28"/>
       <c r="F13" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="205"/>
+      <c r="G13" s="171"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="201"/>
-      <c r="B14" s="200" t="s">
+      <c r="A14" s="189"/>
+      <c r="B14" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="216">
+      <c r="C14" s="182">
         <v>86554</v>
       </c>
       <c r="D14" s="11"/>
@@ -2093,14 +2278,14 @@
       <c r="F14" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="205"/>
+      <c r="G14" s="171"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="201"/>
-      <c r="B15" s="200" t="s">
+      <c r="A15" s="189"/>
+      <c r="B15" s="168" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="216">
+      <c r="C15" s="182">
         <v>767204</v>
       </c>
       <c r="D15" s="11"/>
@@ -2111,13 +2296,13 @@
       <c r="G15" s="24"/>
     </row>
     <row r="16" spans="1:7" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202" t="s">
+      <c r="A16" s="190" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="200" t="s">
+      <c r="B16" s="168" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="215">
+      <c r="C16" s="181">
         <v>17423</v>
       </c>
       <c r="D16" s="11"/>
@@ -2128,11 +2313,11 @@
       <c r="G16" s="24"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
-      <c r="B17" s="200" t="s">
+      <c r="A17" s="190"/>
+      <c r="B17" s="168" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="216">
+      <c r="C17" s="182">
         <v>43687</v>
       </c>
       <c r="D17" s="11"/>
@@ -2141,22 +2326,22 @@
       <c r="G17" s="24"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="202"/>
-      <c r="B18" s="200" t="s">
+      <c r="A18" s="190"/>
+      <c r="B18" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="215"/>
+      <c r="C18" s="181"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="202"/>
-      <c r="B19" s="200" t="s">
+      <c r="A19" s="190"/>
+      <c r="B19" s="168" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="219">
+      <c r="C19" s="185">
         <v>20823</v>
       </c>
       <c r="D19" s="11"/>
@@ -2165,11 +2350,11 @@
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
-      <c r="B20" s="200" t="s">
+      <c r="A20" s="190"/>
+      <c r="B20" s="168" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="215"/>
+      <c r="C20" s="181"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="16"/>
@@ -2177,7 +2362,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
-      <c r="C21" s="204"/>
+      <c r="C21" s="170"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
@@ -2263,7 +2448,7 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="143" t="s">
+      <c r="C1" s="124" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1"/>
@@ -2274,23 +2459,23 @@
       <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="167" t="s">
+      <c r="I1" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="167" t="s">
+      <c r="J1" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="167" t="s">
+      <c r="K1" s="142" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="7"/>
-      <c r="M1" s="191" t="s">
+      <c r="M1" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="191" t="s">
+      <c r="N1" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="191" t="s">
+      <c r="O1" s="162" t="s">
         <v>4</v>
       </c>
       <c r="P1" s="10"/>
@@ -2308,23 +2493,23 @@
       </c>
       <c r="G2" s="24"/>
       <c r="H2" s="16"/>
-      <c r="I2" s="180" t="s">
+      <c r="I2" s="195" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="183" t="s">
+      <c r="J2" s="154" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="168">
+      <c r="K2" s="143">
         <v>1400</v>
       </c>
       <c r="L2" s="16"/>
-      <c r="M2" s="194" t="s">
+      <c r="M2" s="198" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="162" t="s">
+      <c r="N2" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="O2" s="184">
+      <c r="O2" s="155">
         <v>550</v>
       </c>
     </row>
@@ -2341,19 +2526,19 @@
       </c>
       <c r="G3" s="24"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="181"/>
-      <c r="J3" s="170" t="s">
+      <c r="I3" s="196"/>
+      <c r="J3" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="171">
+      <c r="K3" s="145">
         <v>5112</v>
       </c>
       <c r="L3" s="16"/>
-      <c r="M3" s="195"/>
-      <c r="N3" s="162" t="s">
+      <c r="M3" s="199"/>
+      <c r="N3" s="138" t="s">
         <v>170</v>
       </c>
-      <c r="O3" s="184">
+      <c r="O3" s="155">
         <v>4267</v>
       </c>
     </row>
@@ -2370,19 +2555,19 @@
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="181"/>
-      <c r="J4" s="170" t="s">
+      <c r="I4" s="196"/>
+      <c r="J4" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="171">
+      <c r="K4" s="145">
         <v>4743</v>
       </c>
       <c r="L4" s="16"/>
-      <c r="M4" s="195"/>
-      <c r="N4" s="162" t="s">
+      <c r="M4" s="199"/>
+      <c r="N4" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="O4" s="184">
+      <c r="O4" s="155">
         <v>1019.22</v>
       </c>
     </row>
@@ -2391,7 +2576,7 @@
       <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="211"/>
+      <c r="C5" s="177"/>
       <c r="D5" s="11"/>
       <c r="E5" s="28"/>
       <c r="F5" s="13" t="s">
@@ -2399,30 +2584,30 @@
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="170" t="s">
+      <c r="I5" s="196"/>
+      <c r="J5" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="171">
+      <c r="K5" s="145">
         <v>300</v>
       </c>
       <c r="L5" s="16"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="162" t="s">
+      <c r="M5" s="199"/>
+      <c r="N5" s="138" t="s">
         <v>172</v>
       </c>
-      <c r="O5" s="184">
+      <c r="O5" s="155">
         <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="210" t="s">
+      <c r="B6" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="212">
+      <c r="C6" s="178">
         <v>4650</v>
       </c>
       <c r="D6" s="11"/>
@@ -2432,28 +2617,28 @@
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="170" t="s">
+      <c r="I6" s="196"/>
+      <c r="J6" s="144" t="s">
         <v>154</v>
       </c>
-      <c r="K6" s="171">
+      <c r="K6" s="145">
         <v>3710</v>
       </c>
       <c r="L6" s="16"/>
-      <c r="M6" s="195"/>
-      <c r="N6" s="162" t="s">
+      <c r="M6" s="199"/>
+      <c r="N6" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="O6" s="184">
+      <c r="O6" s="155">
         <v>573.49</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="124"/>
-      <c r="B7" s="210" t="s">
+      <c r="A7" s="187"/>
+      <c r="B7" s="176" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="212">
+      <c r="C7" s="178">
         <v>14373</v>
       </c>
       <c r="D7" s="11"/>
@@ -2463,28 +2648,28 @@
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="181"/>
-      <c r="J7" s="170" t="s">
+      <c r="I7" s="196"/>
+      <c r="J7" s="144" t="s">
         <v>155</v>
       </c>
-      <c r="K7" s="171">
+      <c r="K7" s="145">
         <v>270</v>
       </c>
       <c r="L7" s="16"/>
-      <c r="M7" s="195"/>
-      <c r="N7" s="159" t="s">
+      <c r="M7" s="199"/>
+      <c r="N7" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="O7" s="184">
+      <c r="O7" s="155">
         <v>2728</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="125"/>
-      <c r="B8" s="210" t="s">
+      <c r="A8" s="188"/>
+      <c r="B8" s="176" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="212">
+      <c r="C8" s="178">
         <v>13948</v>
       </c>
       <c r="D8" s="11"/>
@@ -2494,28 +2679,28 @@
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="170" t="s">
+      <c r="I8" s="196"/>
+      <c r="J8" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="171">
+      <c r="K8" s="145">
         <v>647</v>
       </c>
       <c r="L8" s="16"/>
-      <c r="M8" s="195"/>
-      <c r="N8" s="159" t="s">
+      <c r="M8" s="199"/>
+      <c r="N8" s="136" t="s">
         <v>175</v>
       </c>
-      <c r="O8" s="185">
+      <c r="O8" s="156">
         <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="210" t="s">
+      <c r="B9" s="176" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="213"/>
+      <c r="C9" s="179"/>
       <c r="D9" s="11"/>
       <c r="E9" s="28"/>
       <c r="F9" s="22" t="s">
@@ -2523,118 +2708,118 @@
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="181"/>
-      <c r="J9" s="170" t="s">
+      <c r="I9" s="196"/>
+      <c r="J9" s="144" t="s">
         <v>156</v>
       </c>
-      <c r="K9" s="171">
+      <c r="K9" s="145">
         <v>500</v>
       </c>
       <c r="L9" s="16"/>
-      <c r="M9" s="195"/>
-      <c r="N9" s="159" t="s">
+      <c r="M9" s="199"/>
+      <c r="N9" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="O9" s="185">
+      <c r="O9" s="156">
         <v>10620</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
-      <c r="B10" s="210" t="s">
+      <c r="B10" s="176" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="213"/>
+      <c r="C10" s="179"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="186" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="209">
+      <c r="G10" s="175">
         <v>32092.7</v>
       </c>
       <c r="H10" s="16"/>
-      <c r="I10" s="181"/>
-      <c r="J10" s="170" t="s">
+      <c r="I10" s="196"/>
+      <c r="J10" s="144" t="s">
         <v>157</v>
       </c>
-      <c r="K10" s="171">
+      <c r="K10" s="145">
         <v>7079</v>
       </c>
       <c r="L10" s="16"/>
-      <c r="M10" s="195"/>
-      <c r="N10" s="159" t="s">
+      <c r="M10" s="199"/>
+      <c r="N10" s="136" t="s">
         <v>177</v>
       </c>
-      <c r="O10" s="185">
+      <c r="O10" s="156">
         <v>1171</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="210" t="s">
+      <c r="B11" s="176" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="213"/>
+      <c r="C11" s="179"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="124"/>
+      <c r="E11" s="187"/>
       <c r="F11" s="27"/>
       <c r="G11" s="24"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="172" t="s">
+      <c r="I11" s="197"/>
+      <c r="J11" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="173">
+      <c r="K11" s="147">
         <f>SUM(K2:K10)</f>
         <v>23761</v>
       </c>
       <c r="L11" s="16"/>
-      <c r="M11" s="195"/>
-      <c r="N11" s="159" t="s">
+      <c r="M11" s="199"/>
+      <c r="N11" s="136" t="s">
         <v>178</v>
       </c>
-      <c r="O11" s="184">
+      <c r="O11" s="155">
         <v>431.54</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
-      <c r="B12" s="210" t="s">
+      <c r="B12" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="213"/>
+      <c r="C12" s="179"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="125"/>
+      <c r="E12" s="188"/>
       <c r="F12" s="13"/>
       <c r="G12" s="24"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="169" t="s">
+      <c r="I12" s="194" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="177" t="s">
+      <c r="J12" s="151" t="s">
         <v>158</v>
       </c>
-      <c r="K12" s="175">
+      <c r="K12" s="149">
         <v>45000</v>
       </c>
       <c r="L12" s="16"/>
-      <c r="M12" s="195"/>
-      <c r="N12" s="159" t="s">
+      <c r="M12" s="199"/>
+      <c r="N12" s="136" t="s">
         <v>179</v>
       </c>
-      <c r="O12" s="185">
+      <c r="O12" s="156">
         <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
-      <c r="B13" s="210" t="s">
+      <c r="B13" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="213"/>
+      <c r="C13" s="179"/>
       <c r="D13" s="11"/>
       <c r="E13" s="28"/>
       <c r="F13" s="13" t="s">
@@ -2642,28 +2827,28 @@
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="169"/>
-      <c r="J13" s="177" t="s">
+      <c r="I13" s="194"/>
+      <c r="J13" s="151" t="s">
         <v>159</v>
       </c>
-      <c r="K13" s="175">
+      <c r="K13" s="149">
         <v>27000</v>
       </c>
       <c r="L13" s="16"/>
-      <c r="M13" s="195"/>
-      <c r="N13" s="159" t="s">
+      <c r="M13" s="199"/>
+      <c r="N13" s="136" t="s">
         <v>180</v>
       </c>
-      <c r="O13" s="184">
+      <c r="O13" s="155">
         <v>682.04</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
-      <c r="B14" s="210" t="s">
+      <c r="B14" s="176" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="212">
+      <c r="C14" s="178">
         <v>69302</v>
       </c>
       <c r="D14" s="11"/>
@@ -2673,28 +2858,28 @@
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="169"/>
-      <c r="J14" s="179" t="s">
+      <c r="I14" s="194"/>
+      <c r="J14" s="153" t="s">
         <v>160</v>
       </c>
-      <c r="K14" s="175">
+      <c r="K14" s="149">
         <v>15000</v>
       </c>
       <c r="L14" s="16"/>
-      <c r="M14" s="195"/>
-      <c r="N14" s="162" t="s">
+      <c r="M14" s="199"/>
+      <c r="N14" s="138" t="s">
         <v>181</v>
       </c>
-      <c r="O14" s="184">
+      <c r="O14" s="155">
         <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
-      <c r="B15" s="210" t="s">
+      <c r="B15" s="176" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="212">
+      <c r="C15" s="178">
         <v>676076</v>
       </c>
       <c r="D15" s="11"/>
@@ -2704,30 +2889,30 @@
       </c>
       <c r="G15" s="24"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="169"/>
-      <c r="J15" s="177" t="s">
+      <c r="I15" s="194"/>
+      <c r="J15" s="151" t="s">
         <v>161</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="149">
         <v>6000</v>
       </c>
       <c r="L15" s="16"/>
-      <c r="M15" s="195"/>
-      <c r="N15" s="162" t="s">
+      <c r="M15" s="199"/>
+      <c r="N15" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="O15" s="162">
+      <c r="O15" s="138">
         <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="129" t="s">
+      <c r="A16" s="202" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="210" t="s">
+      <c r="B16" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="213">
+      <c r="C16" s="179">
         <v>23761</v>
       </c>
       <c r="D16" s="11"/>
@@ -2737,28 +2922,28 @@
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="169"/>
-      <c r="J16" s="177" t="s">
+      <c r="I16" s="194"/>
+      <c r="J16" s="151" t="s">
         <v>162</v>
       </c>
-      <c r="K16" s="176">
+      <c r="K16" s="150">
         <v>1490</v>
       </c>
       <c r="L16" s="16"/>
-      <c r="M16" s="195"/>
-      <c r="N16" s="162" t="s">
+      <c r="M16" s="199"/>
+      <c r="N16" s="138" t="s">
         <v>183</v>
       </c>
-      <c r="O16" s="162">
+      <c r="O16" s="138">
         <v>1758.2</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="210" t="s">
+      <c r="A17" s="187"/>
+      <c r="B17" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="214">
+      <c r="C17" s="180">
         <v>46881</v>
       </c>
       <c r="D17" s="11"/>
@@ -2766,46 +2951,46 @@
       <c r="F17" s="30"/>
       <c r="G17" s="24"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="179" t="s">
+      <c r="I17" s="194"/>
+      <c r="J17" s="153" t="s">
         <v>163</v>
       </c>
-      <c r="K17" s="176">
+      <c r="K17" s="150">
         <v>220</v>
       </c>
       <c r="L17" s="16"/>
-      <c r="M17" s="195"/>
-      <c r="N17" s="162" t="s">
+      <c r="M17" s="199"/>
+      <c r="N17" s="138" t="s">
         <v>184</v>
       </c>
-      <c r="O17" s="162">
+      <c r="O17" s="138">
         <v>409.22</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="125"/>
-      <c r="B18" s="210" t="s">
+      <c r="A18" s="188"/>
+      <c r="B18" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="213"/>
+      <c r="C18" s="179"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="169"/>
-      <c r="J18" s="177" t="s">
+      <c r="I18" s="194"/>
+      <c r="J18" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="K18" s="175">
+      <c r="K18" s="149">
         <v>7417</v>
       </c>
       <c r="L18" s="16"/>
-      <c r="M18" s="195"/>
-      <c r="N18" s="162" t="s">
+      <c r="M18" s="199"/>
+      <c r="N18" s="138" t="s">
         <v>181</v>
       </c>
-      <c r="O18" s="162">
+      <c r="O18" s="138">
         <v>1000</v>
       </c>
     </row>
@@ -2814,7 +2999,7 @@
       <c r="B19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="203">
+      <c r="C19" s="169">
         <v>125627</v>
       </c>
       <c r="D19" s="11"/>
@@ -2822,19 +3007,19 @@
       <c r="F19" s="16"/>
       <c r="G19" s="11"/>
       <c r="H19" s="16"/>
-      <c r="I19" s="169"/>
-      <c r="J19" s="177" t="s">
+      <c r="I19" s="194"/>
+      <c r="J19" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="K19" s="175">
+      <c r="K19" s="149">
         <v>14500</v>
       </c>
       <c r="L19" s="16"/>
-      <c r="M19" s="196"/>
-      <c r="N19" s="192" t="s">
+      <c r="M19" s="200"/>
+      <c r="N19" s="163" t="s">
         <v>77</v>
       </c>
-      <c r="O19" s="193">
+      <c r="O19" s="164">
         <v>32092.7</v>
       </c>
     </row>
@@ -2843,23 +3028,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="208"/>
+      <c r="C20" s="174"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="16"/>
       <c r="G20" s="11"/>
       <c r="H20" s="16"/>
-      <c r="I20" s="169"/>
-      <c r="J20" s="177" t="s">
+      <c r="I20" s="194"/>
+      <c r="J20" s="151" t="s">
         <v>166</v>
       </c>
-      <c r="K20" s="168">
+      <c r="K20" s="143">
         <v>5000</v>
       </c>
       <c r="L20" s="16"/>
-      <c r="M20" s="186"/>
-      <c r="N20" s="187"/>
-      <c r="O20" s="188"/>
+      <c r="M20" s="157"/>
+      <c r="N20" s="158"/>
+      <c r="O20" s="159"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
@@ -2870,17 +3055,17 @@
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
-      <c r="I21" s="169"/>
-      <c r="J21" s="177" t="s">
+      <c r="I21" s="194"/>
+      <c r="J21" s="151" t="s">
         <v>167</v>
       </c>
-      <c r="K21" s="168">
+      <c r="K21" s="143">
         <v>1000</v>
       </c>
       <c r="L21" s="16"/>
-      <c r="M21" s="186"/>
-      <c r="N21" s="189"/>
-      <c r="O21" s="189"/>
+      <c r="M21" s="157"/>
+      <c r="N21" s="160"/>
+      <c r="O21" s="160"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
@@ -2891,17 +3076,17 @@
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
-      <c r="I22" s="169"/>
-      <c r="J22" s="177" t="s">
+      <c r="I22" s="194"/>
+      <c r="J22" s="151" t="s">
         <v>168</v>
       </c>
-      <c r="K22" s="168">
+      <c r="K22" s="143">
         <v>3000</v>
       </c>
       <c r="L22" s="16"/>
-      <c r="M22" s="186"/>
-      <c r="N22" s="189"/>
-      <c r="O22" s="189"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="160"/>
+      <c r="O22" s="160"/>
     </row>
     <row r="23" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
@@ -2912,18 +3097,18 @@
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
-      <c r="I23" s="169"/>
-      <c r="J23" s="178" t="s">
+      <c r="I23" s="194"/>
+      <c r="J23" s="152" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="174">
+      <c r="K23" s="148">
         <f>SUM(K12:K22)</f>
         <v>125627</v>
       </c>
       <c r="L23" s="16"/>
-      <c r="M23" s="186"/>
-      <c r="N23" s="189"/>
-      <c r="O23" s="189"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="160"/>
+      <c r="O23" s="160"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
@@ -2934,11 +3119,11 @@
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
-      <c r="I24" s="166"/>
+      <c r="I24" s="141"/>
       <c r="L24" s="16"/>
-      <c r="M24" s="186"/>
-      <c r="N24" s="189"/>
-      <c r="O24" s="189"/>
+      <c r="M24" s="157"/>
+      <c r="N24" s="160"/>
+      <c r="O24" s="160"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
@@ -2953,9 +3138,9 @@
       <c r="J25" s="31"/>
       <c r="K25" s="31"/>
       <c r="L25" s="16"/>
-      <c r="M25" s="186"/>
-      <c r="N25" s="189"/>
-      <c r="O25" s="189"/>
+      <c r="M25" s="157"/>
+      <c r="N25" s="160"/>
+      <c r="O25" s="160"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
@@ -2970,9 +3155,9 @@
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="186"/>
-      <c r="N26" s="189"/>
-      <c r="O26" s="189"/>
+      <c r="M26" s="157"/>
+      <c r="N26" s="160"/>
+      <c r="O26" s="160"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
@@ -2987,9 +3172,9 @@
       <c r="J27" s="31"/>
       <c r="K27" s="31"/>
       <c r="L27" s="16"/>
-      <c r="M27" s="186"/>
-      <c r="N27" s="189"/>
-      <c r="O27" s="189"/>
+      <c r="M27" s="157"/>
+      <c r="N27" s="160"/>
+      <c r="O27" s="160"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
@@ -3004,9 +3189,9 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
       <c r="L28" s="16"/>
-      <c r="M28" s="186"/>
-      <c r="N28" s="189"/>
-      <c r="O28" s="189"/>
+      <c r="M28" s="157"/>
+      <c r="N28" s="160"/>
+      <c r="O28" s="160"/>
     </row>
     <row r="29" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
@@ -3021,20 +3206,20 @@
       <c r="J29" s="31"/>
       <c r="K29" s="31"/>
       <c r="L29" s="16"/>
-      <c r="M29" s="186"/>
-      <c r="N29" s="187"/>
-      <c r="O29" s="187"/>
+      <c r="M29" s="157"/>
+      <c r="N29" s="158"/>
+      <c r="O29" s="158"/>
     </row>
     <row r="30" spans="1:15" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D30" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="147" t="s">
+      <c r="E30" s="128" t="s">
         <v>84</v>
       </c>
       <c r="F30" s="16"/>
@@ -3044,18 +3229,18 @@
       <c r="J30" s="31"/>
       <c r="K30" s="31"/>
       <c r="L30" s="16"/>
-      <c r="M30" s="186"/>
-      <c r="N30" s="189"/>
-      <c r="O30" s="189"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="160"/>
+      <c r="O30" s="160"/>
     </row>
     <row r="31" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="149" t="s">
+      <c r="C31" s="129"/>
+      <c r="D31" s="130" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="150">
+      <c r="E31" s="131">
         <v>1400</v>
       </c>
       <c r="F31" s="16"/>
@@ -3065,20 +3250,20 @@
       <c r="J31" s="31"/>
       <c r="K31" s="31"/>
       <c r="L31" s="16"/>
-      <c r="M31" s="186"/>
-      <c r="N31" s="189"/>
-      <c r="O31" s="189"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="160"/>
+      <c r="O31" s="160"/>
     </row>
     <row r="32" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
-      <c r="C32" s="151" t="s">
+      <c r="C32" s="203" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="152" t="s">
+      <c r="D32" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="153">
+      <c r="E32" s="133">
         <v>5112</v>
       </c>
       <c r="F32" s="16"/>
@@ -3088,18 +3273,18 @@
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
       <c r="L32" s="16"/>
-      <c r="M32" s="186"/>
-      <c r="N32" s="189"/>
-      <c r="O32" s="189"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="160"/>
     </row>
     <row r="33" spans="1:15" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="16"/>
-      <c r="C33" s="154"/>
-      <c r="D33" s="152" t="s">
+      <c r="C33" s="204"/>
+      <c r="D33" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="153">
+      <c r="E33" s="133">
         <v>4743</v>
       </c>
       <c r="F33" s="16"/>
@@ -3109,18 +3294,18 @@
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
       <c r="L33" s="16"/>
-      <c r="M33" s="186"/>
-      <c r="N33" s="189"/>
-      <c r="O33" s="189"/>
+      <c r="M33" s="157"/>
+      <c r="N33" s="160"/>
+      <c r="O33" s="160"/>
     </row>
     <row r="34" spans="1:15" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="152" t="s">
+      <c r="C34" s="204"/>
+      <c r="D34" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="153">
+      <c r="E34" s="133">
         <v>300</v>
       </c>
       <c r="F34" s="16"/>
@@ -3130,18 +3315,18 @@
       <c r="J34" s="31"/>
       <c r="K34" s="31"/>
       <c r="L34" s="16"/>
-      <c r="M34" s="186"/>
-      <c r="N34" s="189"/>
-      <c r="O34" s="189"/>
+      <c r="M34" s="157"/>
+      <c r="N34" s="160"/>
+      <c r="O34" s="160"/>
     </row>
     <row r="35" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="154"/>
-      <c r="D35" s="152" t="s">
+      <c r="C35" s="204"/>
+      <c r="D35" s="132" t="s">
         <v>154</v>
       </c>
-      <c r="E35" s="153">
+      <c r="E35" s="133">
         <v>3710</v>
       </c>
       <c r="F35" s="16"/>
@@ -3151,18 +3336,18 @@
       <c r="J35" s="31"/>
       <c r="K35" s="31"/>
       <c r="L35" s="16"/>
-      <c r="M35" s="186"/>
-      <c r="N35" s="189"/>
-      <c r="O35" s="189"/>
+      <c r="M35" s="157"/>
+      <c r="N35" s="160"/>
+      <c r="O35" s="160"/>
     </row>
     <row r="36" spans="1:15" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="152" t="s">
+      <c r="C36" s="204"/>
+      <c r="D36" s="132" t="s">
         <v>155</v>
       </c>
-      <c r="E36" s="153">
+      <c r="E36" s="133">
         <v>270</v>
       </c>
       <c r="F36" s="16"/>
@@ -3172,18 +3357,18 @@
       <c r="J36" s="31"/>
       <c r="K36" s="31"/>
       <c r="L36" s="16"/>
-      <c r="M36" s="186"/>
-      <c r="N36" s="189"/>
-      <c r="O36" s="189"/>
+      <c r="M36" s="157"/>
+      <c r="N36" s="160"/>
+      <c r="O36" s="160"/>
     </row>
     <row r="37" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
-      <c r="C37" s="154"/>
-      <c r="D37" s="152" t="s">
+      <c r="C37" s="204"/>
+      <c r="D37" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="153">
+      <c r="E37" s="133">
         <v>647</v>
       </c>
       <c r="F37" s="16"/>
@@ -3193,18 +3378,18 @@
       <c r="J37" s="31"/>
       <c r="K37" s="31"/>
       <c r="L37" s="16"/>
-      <c r="M37" s="186"/>
-      <c r="N37" s="187"/>
-      <c r="O37" s="187"/>
+      <c r="M37" s="157"/>
+      <c r="N37" s="158"/>
+      <c r="O37" s="158"/>
     </row>
     <row r="38" spans="1:15" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
-      <c r="C38" s="154"/>
-      <c r="D38" s="152" t="s">
+      <c r="C38" s="204"/>
+      <c r="D38" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="153">
+      <c r="E38" s="133">
         <v>500</v>
       </c>
       <c r="F38" s="16"/>
@@ -3214,139 +3399,139 @@
       <c r="J38" s="31"/>
       <c r="K38" s="31"/>
       <c r="L38" s="16"/>
-      <c r="M38" s="190"/>
-      <c r="N38" s="187"/>
-      <c r="O38" s="187"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="158"/>
+      <c r="O38" s="158"/>
     </row>
     <row r="39" spans="1:15" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="154"/>
-      <c r="D39" s="152" t="s">
+      <c r="C39" s="204"/>
+      <c r="D39" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="153">
+      <c r="E39" s="133">
         <v>7079</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="155"/>
-      <c r="D40" s="156" t="s">
+      <c r="C40" s="205"/>
+      <c r="D40" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="E40" s="157">
+      <c r="E40" s="135">
         <f>SUM(E31:E39)</f>
         <v>23761</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C41" s="158" t="s">
+      <c r="C41" s="191" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="159" t="s">
+      <c r="D41" s="136" t="s">
         <v>158</v>
       </c>
-      <c r="E41" s="160">
+      <c r="E41" s="137">
         <v>45000</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C42" s="161"/>
-      <c r="D42" s="159" t="s">
+      <c r="C42" s="192"/>
+      <c r="D42" s="136" t="s">
         <v>159</v>
       </c>
-      <c r="E42" s="160">
+      <c r="E42" s="137">
         <v>27000</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C43" s="161"/>
-      <c r="D43" s="159"/>
-      <c r="E43" s="160"/>
+      <c r="C43" s="192"/>
+      <c r="D43" s="136"/>
+      <c r="E43" s="137"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C44" s="161"/>
-      <c r="D44" s="162" t="s">
+      <c r="C44" s="192"/>
+      <c r="D44" s="138" t="s">
         <v>160</v>
       </c>
-      <c r="E44" s="160">
+      <c r="E44" s="137">
         <v>15000</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C45" s="161"/>
-      <c r="D45" s="159" t="s">
+      <c r="C45" s="192"/>
+      <c r="D45" s="136" t="s">
         <v>161</v>
       </c>
-      <c r="E45" s="160">
+      <c r="E45" s="137">
         <v>6000</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="163"/>
-      <c r="D46" s="159" t="s">
+      <c r="C46" s="193"/>
+      <c r="D46" s="136" t="s">
         <v>162</v>
       </c>
-      <c r="E46" s="164">
+      <c r="E46" s="139">
         <v>1490</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C47" s="148"/>
-      <c r="D47" s="162" t="s">
+      <c r="C47" s="129"/>
+      <c r="D47" s="138" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="164">
+      <c r="E47" s="139">
         <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C48" s="148"/>
-      <c r="D48" s="159" t="s">
+      <c r="C48" s="129"/>
+      <c r="D48" s="136" t="s">
         <v>164</v>
       </c>
-      <c r="E48" s="150">
+      <c r="E48" s="131">
         <v>7417</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C49" s="148"/>
-      <c r="D49" s="165" t="s">
+      <c r="C49" s="129"/>
+      <c r="D49" s="140" t="s">
         <v>165</v>
       </c>
-      <c r="E49" s="150">
+      <c r="E49" s="131">
         <v>14500</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C50" s="148"/>
-      <c r="D50" s="165" t="s">
+      <c r="C50" s="129"/>
+      <c r="D50" s="140" t="s">
         <v>166</v>
       </c>
-      <c r="E50" s="150">
+      <c r="E50" s="131">
         <v>5000</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C51" s="148"/>
-      <c r="D51" s="165" t="s">
+      <c r="C51" s="129"/>
+      <c r="D51" s="140" t="s">
         <v>167</v>
       </c>
-      <c r="E51" s="150">
+      <c r="E51" s="131">
         <v>1000</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C52" s="148"/>
-      <c r="D52" s="165" t="s">
+      <c r="C52" s="129"/>
+      <c r="D52" s="140" t="s">
         <v>168</v>
       </c>
-      <c r="E52" s="150">
+      <c r="E52" s="131">
         <v>3000</v>
       </c>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C53" s="148"/>
-      <c r="D53" s="149"/>
-      <c r="E53" s="150">
+      <c r="C53" s="129"/>
+      <c r="D53" s="130"/>
+      <c r="E53" s="131">
         <f>SUM(E41:E52)</f>
         <v>125627</v>
       </c>
@@ -3376,7 +3561,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.90625" customWidth="1"/>
-    <col min="3" max="3" width="21.26953125" style="145" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" style="126" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="9" max="9" width="21.90625" customWidth="1"/>
     <col min="10" max="10" width="27.453125" customWidth="1"/>
@@ -3388,7 +3573,7 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="143" t="s">
+      <c r="C1" s="124" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1"/>
@@ -3433,7 +3618,7 @@
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="16"/>
-      <c r="I2" s="123" t="s">
+      <c r="I2" s="206" t="s">
         <v>7</v>
       </c>
       <c r="J2" s="17" t="s">
@@ -3443,7 +3628,7 @@
         <v>1480</v>
       </c>
       <c r="L2" s="16"/>
-      <c r="M2" s="126" t="s">
+      <c r="M2" s="207" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="18" t="s">
@@ -3466,7 +3651,7 @@
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="124"/>
+      <c r="I3" s="187"/>
       <c r="J3" s="18" t="s">
         <v>13</v>
       </c>
@@ -3474,7 +3659,7 @@
         <v>3782</v>
       </c>
       <c r="L3" s="16"/>
-      <c r="M3" s="124"/>
+      <c r="M3" s="187"/>
       <c r="N3" s="18" t="s">
         <v>14</v>
       </c>
@@ -3495,7 +3680,7 @@
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="16"/>
-      <c r="I4" s="124"/>
+      <c r="I4" s="187"/>
       <c r="J4" s="18" t="s">
         <v>17</v>
       </c>
@@ -3503,7 +3688,7 @@
         <v>300</v>
       </c>
       <c r="L4" s="16"/>
-      <c r="M4" s="124"/>
+      <c r="M4" s="187"/>
       <c r="N4" s="18" t="s">
         <v>14</v>
       </c>
@@ -3524,7 +3709,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="124"/>
+      <c r="I5" s="187"/>
       <c r="J5" s="18" t="s">
         <v>20</v>
       </c>
@@ -3532,7 +3717,7 @@
         <v>1200</v>
       </c>
       <c r="L5" s="16"/>
-      <c r="M5" s="124"/>
+      <c r="M5" s="187"/>
       <c r="N5" s="18" t="s">
         <v>21</v>
       </c>
@@ -3541,13 +3726,13 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="201" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="144">
+      <c r="C6" s="125">
         <v>6500</v>
       </c>
       <c r="D6" s="11"/>
@@ -3557,7 +3742,7 @@
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="124"/>
+      <c r="I6" s="187"/>
       <c r="J6" s="18" t="s">
         <v>25</v>
       </c>
@@ -3565,7 +3750,7 @@
         <v>1860</v>
       </c>
       <c r="L6" s="16"/>
-      <c r="M6" s="124"/>
+      <c r="M6" s="187"/>
       <c r="N6" s="18" t="s">
         <v>26</v>
       </c>
@@ -3574,7 +3759,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="124"/>
+      <c r="A7" s="187"/>
       <c r="B7" s="12" t="s">
         <v>27</v>
       </c>
@@ -3586,7 +3771,7 @@
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="124"/>
+      <c r="I7" s="187"/>
       <c r="J7" s="18" t="s">
         <v>29</v>
       </c>
@@ -3594,7 +3779,7 @@
         <v>1440</v>
       </c>
       <c r="L7" s="16"/>
-      <c r="M7" s="124"/>
+      <c r="M7" s="187"/>
       <c r="N7" s="18" t="s">
         <v>26</v>
       </c>
@@ -3603,11 +3788,11 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="125"/>
+      <c r="A8" s="188"/>
       <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="144">
+      <c r="C8" s="125">
         <v>13948</v>
       </c>
       <c r="D8" s="11"/>
@@ -3617,7 +3802,7 @@
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="124"/>
+      <c r="I8" s="187"/>
       <c r="J8" s="18" t="s">
         <v>32</v>
       </c>
@@ -3625,7 +3810,7 @@
         <v>535</v>
       </c>
       <c r="L8" s="16"/>
-      <c r="M8" s="124"/>
+      <c r="M8" s="187"/>
       <c r="N8" s="18" t="s">
         <v>26</v>
       </c>
@@ -3646,7 +3831,7 @@
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="124"/>
+      <c r="I9" s="187"/>
       <c r="J9" s="23" t="s">
         <v>35</v>
       </c>
@@ -3654,7 +3839,7 @@
         <v>5899</v>
       </c>
       <c r="L9" s="16"/>
-      <c r="M9" s="124"/>
+      <c r="M9" s="187"/>
       <c r="N9" s="18" t="s">
         <v>36</v>
       </c>
@@ -3669,7 +3854,7 @@
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="128" t="s">
+      <c r="E10" s="186" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -3679,7 +3864,7 @@
         <v>106739</v>
       </c>
       <c r="H10" s="16"/>
-      <c r="I10" s="125"/>
+      <c r="I10" s="188"/>
       <c r="J10" s="25" t="s">
         <v>40</v>
       </c>
@@ -3688,7 +3873,7 @@
         <v>16496</v>
       </c>
       <c r="L10" s="16"/>
-      <c r="M10" s="124"/>
+      <c r="M10" s="187"/>
       <c r="N10" s="18" t="s">
         <v>41</v>
       </c>
@@ -3703,11 +3888,11 @@
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="124"/>
+      <c r="E11" s="187"/>
       <c r="F11" s="27"/>
       <c r="G11" s="15"/>
       <c r="H11" s="16"/>
-      <c r="I11" s="126" t="s">
+      <c r="I11" s="207" t="s">
         <v>43</v>
       </c>
       <c r="J11" s="18" t="s">
@@ -3717,7 +3902,7 @@
         <v>3024</v>
       </c>
       <c r="L11" s="16"/>
-      <c r="M11" s="124"/>
+      <c r="M11" s="187"/>
       <c r="N11" s="18" t="s">
         <v>41</v>
       </c>
@@ -3732,11 +3917,11 @@
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="125"/>
+      <c r="E12" s="188"/>
       <c r="F12" s="13"/>
       <c r="G12" s="15"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="124"/>
+      <c r="I12" s="187"/>
       <c r="J12" s="18" t="s">
         <v>46</v>
       </c>
@@ -3744,7 +3929,7 @@
         <v>3000</v>
       </c>
       <c r="L12" s="16"/>
-      <c r="M12" s="124"/>
+      <c r="M12" s="187"/>
       <c r="N12" s="18" t="s">
         <v>41</v>
       </c>
@@ -3765,7 +3950,7 @@
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="124"/>
+      <c r="I13" s="187"/>
       <c r="J13" s="18" t="s">
         <v>49</v>
       </c>
@@ -3773,7 +3958,7 @@
         <v>4007</v>
       </c>
       <c r="L13" s="16"/>
-      <c r="M13" s="124"/>
+      <c r="M13" s="187"/>
       <c r="N13" s="18" t="s">
         <v>41</v>
       </c>
@@ -3786,7 +3971,7 @@
       <c r="B14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="144">
+      <c r="C14" s="125">
         <v>79939.199999999997</v>
       </c>
       <c r="D14" s="11"/>
@@ -3796,7 +3981,7 @@
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="124"/>
+      <c r="I14" s="187"/>
       <c r="J14" s="18" t="s">
         <v>52</v>
       </c>
@@ -3804,7 +3989,7 @@
         <v>10200</v>
       </c>
       <c r="L14" s="16"/>
-      <c r="M14" s="124"/>
+      <c r="M14" s="187"/>
       <c r="N14" s="18" t="s">
         <v>53</v>
       </c>
@@ -3817,7 +4002,7 @@
       <c r="B15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="144">
+      <c r="C15" s="125">
         <v>832770</v>
       </c>
       <c r="D15" s="11"/>
@@ -3827,7 +4012,7 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="125"/>
+      <c r="I15" s="188"/>
       <c r="J15" s="25" t="s">
         <v>40</v>
       </c>
@@ -3836,7 +4021,7 @@
         <v>20231</v>
       </c>
       <c r="L15" s="16"/>
-      <c r="M15" s="124"/>
+      <c r="M15" s="187"/>
       <c r="N15" s="18" t="s">
         <v>56</v>
       </c>
@@ -3845,7 +4030,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="129" t="s">
+      <c r="A16" s="202" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -3865,7 +4050,7 @@
       <c r="J16" s="29"/>
       <c r="K16" s="29"/>
       <c r="L16" s="16"/>
-      <c r="M16" s="124"/>
+      <c r="M16" s="187"/>
       <c r="N16" s="18" t="s">
         <v>60</v>
       </c>
@@ -3874,7 +4059,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
+      <c r="A17" s="187"/>
       <c r="B17" s="12" t="s">
         <v>61</v>
       </c>
@@ -3888,7 +4073,7 @@
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
       <c r="L17" s="16"/>
-      <c r="M17" s="124"/>
+      <c r="M17" s="187"/>
       <c r="N17" s="18" t="s">
         <v>62</v>
       </c>
@@ -3897,7 +4082,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="125"/>
+      <c r="A18" s="188"/>
       <c r="B18" s="12" t="s">
         <v>63</v>
       </c>
@@ -3911,7 +4096,7 @@
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
       <c r="L18" s="16"/>
-      <c r="M18" s="124"/>
+      <c r="M18" s="187"/>
       <c r="N18" s="18" t="s">
         <v>64</v>
       </c>
@@ -3936,7 +4121,7 @@
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
       <c r="L19" s="16"/>
-      <c r="M19" s="124"/>
+      <c r="M19" s="187"/>
       <c r="N19" s="18" t="s">
         <v>66</v>
       </c>
@@ -3959,7 +4144,7 @@
       <c r="J20" s="31"/>
       <c r="K20" s="31"/>
       <c r="L20" s="16"/>
-      <c r="M20" s="124"/>
+      <c r="M20" s="187"/>
       <c r="N20" s="18" t="s">
         <v>68</v>
       </c>
@@ -3980,7 +4165,7 @@
       <c r="J21" s="31"/>
       <c r="K21" s="31"/>
       <c r="L21" s="16"/>
-      <c r="M21" s="124"/>
+      <c r="M21" s="187"/>
       <c r="N21" s="18" t="s">
         <v>69</v>
       </c>
@@ -4001,7 +4186,7 @@
       <c r="J22" s="31"/>
       <c r="K22" s="31"/>
       <c r="L22" s="16"/>
-      <c r="M22" s="124"/>
+      <c r="M22" s="187"/>
       <c r="N22" s="18" t="s">
         <v>70</v>
       </c>
@@ -4022,7 +4207,7 @@
       <c r="J23" s="31"/>
       <c r="K23" s="31"/>
       <c r="L23" s="16"/>
-      <c r="M23" s="124"/>
+      <c r="M23" s="187"/>
       <c r="N23" s="18" t="s">
         <v>60</v>
       </c>
@@ -4043,7 +4228,7 @@
       <c r="J24" s="31"/>
       <c r="K24" s="31"/>
       <c r="L24" s="16"/>
-      <c r="M24" s="124"/>
+      <c r="M24" s="187"/>
       <c r="N24" s="18" t="s">
         <v>71</v>
       </c>
@@ -4064,7 +4249,7 @@
       <c r="J25" s="31"/>
       <c r="K25" s="31"/>
       <c r="L25" s="16"/>
-      <c r="M25" s="124"/>
+      <c r="M25" s="187"/>
       <c r="N25" s="18" t="s">
         <v>60</v>
       </c>
@@ -4085,7 +4270,7 @@
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="124"/>
+      <c r="M26" s="187"/>
       <c r="N26" s="18" t="s">
         <v>72</v>
       </c>
@@ -4106,7 +4291,7 @@
       <c r="J27" s="31"/>
       <c r="K27" s="31"/>
       <c r="L27" s="16"/>
-      <c r="M27" s="124"/>
+      <c r="M27" s="187"/>
       <c r="N27" s="18" t="s">
         <v>73</v>
       </c>
@@ -4127,7 +4312,7 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
       <c r="L28" s="16"/>
-      <c r="M28" s="124"/>
+      <c r="M28" s="187"/>
       <c r="N28" s="18" t="s">
         <v>60</v>
       </c>
@@ -4148,7 +4333,7 @@
       <c r="J29" s="31"/>
       <c r="K29" s="31"/>
       <c r="L29" s="16"/>
-      <c r="M29" s="124"/>
+      <c r="M29" s="187"/>
       <c r="N29" s="18" t="s">
         <v>68</v>
       </c>
@@ -4169,7 +4354,7 @@
       <c r="J30" s="31"/>
       <c r="K30" s="31"/>
       <c r="L30" s="16"/>
-      <c r="M30" s="124"/>
+      <c r="M30" s="187"/>
       <c r="N30" s="18" t="s">
         <v>74</v>
       </c>
@@ -4190,7 +4375,7 @@
       <c r="J31" s="31"/>
       <c r="K31" s="31"/>
       <c r="L31" s="16"/>
-      <c r="M31" s="124"/>
+      <c r="M31" s="187"/>
       <c r="N31" s="18" t="s">
         <v>75</v>
       </c>
@@ -4211,7 +4396,7 @@
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
       <c r="L32" s="16"/>
-      <c r="M32" s="124"/>
+      <c r="M32" s="187"/>
       <c r="N32" s="18" t="s">
         <v>70</v>
       </c>
@@ -4232,7 +4417,7 @@
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
       <c r="L33" s="16"/>
-      <c r="M33" s="124"/>
+      <c r="M33" s="187"/>
       <c r="N33" s="18" t="s">
         <v>71</v>
       </c>
@@ -4253,7 +4438,7 @@
       <c r="J34" s="31"/>
       <c r="K34" s="31"/>
       <c r="L34" s="16"/>
-      <c r="M34" s="124"/>
+      <c r="M34" s="187"/>
       <c r="N34" s="18" t="s">
         <v>71</v>
       </c>
@@ -4274,7 +4459,7 @@
       <c r="J35" s="31"/>
       <c r="K35" s="31"/>
       <c r="L35" s="16"/>
-      <c r="M35" s="124"/>
+      <c r="M35" s="187"/>
       <c r="N35" s="18" t="s">
         <v>76</v>
       </c>
@@ -4295,7 +4480,7 @@
       <c r="J36" s="31"/>
       <c r="K36" s="31"/>
       <c r="L36" s="16"/>
-      <c r="M36" s="124"/>
+      <c r="M36" s="187"/>
       <c r="N36" s="18" t="s">
         <v>66</v>
       </c>
@@ -4316,7 +4501,7 @@
       <c r="J37" s="31"/>
       <c r="K37" s="31"/>
       <c r="L37" s="16"/>
-      <c r="M37" s="125"/>
+      <c r="M37" s="188"/>
       <c r="N37" s="34" t="s">
         <v>77</v>
       </c>
@@ -8383,7 +8568,7 @@
       <c r="M6" s="46"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="208" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -8408,7 +8593,7 @@
       <c r="M7" s="46"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="124"/>
+      <c r="A8" s="187"/>
       <c r="B8" s="38" t="s">
         <v>27</v>
       </c>
@@ -8426,7 +8611,7 @@
       <c r="M8" s="54"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="125"/>
+      <c r="A9" s="188"/>
       <c r="B9" s="38" t="s">
         <v>30</v>
       </c>
@@ -8478,7 +8663,7 @@
       </c>
       <c r="C11" s="39"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="131" t="s">
+      <c r="E11" s="209" t="s">
         <v>38</v>
       </c>
       <c r="F11" s="38" t="s">
@@ -8498,7 +8683,7 @@
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="124"/>
+      <c r="E12" s="187"/>
       <c r="F12" s="64"/>
       <c r="G12" s="40"/>
       <c r="I12" s="65" t="s">
@@ -8516,7 +8701,7 @@
       </c>
       <c r="C13" s="39"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="125"/>
+      <c r="E13" s="188"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
       <c r="I13" s="66" t="s">
@@ -8594,7 +8779,7 @@
       <c r="M16" s="46"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="210" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="38" t="s">
@@ -8621,7 +8806,7 @@
       <c r="M17" s="46"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="124"/>
+      <c r="A18" s="187"/>
       <c r="B18" s="38" t="s">
         <v>61</v>
       </c>
@@ -8641,7 +8826,7 @@
       <c r="M18" s="59"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="125"/>
+      <c r="A19" s="188"/>
       <c r="B19" s="38" t="s">
         <v>63</v>
       </c>
@@ -8950,14 +9135,14 @@
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="133" t="s">
+      <c r="I3" s="211" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="134"/>
-      <c r="L3" s="135" t="s">
+      <c r="J3" s="212"/>
+      <c r="L3" s="213" t="s">
         <v>112</v>
       </c>
-      <c r="M3" s="134"/>
+      <c r="M3" s="212"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
@@ -9065,7 +9250,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="214" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="94" t="s">
@@ -9091,7 +9276,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="124"/>
+      <c r="A9" s="187"/>
       <c r="B9" s="94" t="s">
         <v>27</v>
       </c>
@@ -9122,7 +9307,7 @@
       <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
+      <c r="A10" s="188"/>
       <c r="B10" s="94" t="s">
         <v>30</v>
       </c>
@@ -9192,7 +9377,7 @@
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="136" t="s">
+      <c r="E12" s="214" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="38" t="s">
@@ -9224,7 +9409,7 @@
       </c>
       <c r="C13" s="40"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="124"/>
+      <c r="E13" s="187"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
       <c r="I13" s="49" t="s">
@@ -9252,7 +9437,7 @@
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="125"/>
+      <c r="E14" s="188"/>
       <c r="F14" s="39"/>
       <c r="G14" s="40"/>
       <c r="I14" s="52"/>
@@ -9345,7 +9530,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="136" t="s">
+      <c r="A18" s="214" t="s">
         <v>57</v>
       </c>
       <c r="B18" s="94" t="s">
@@ -9375,7 +9560,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="124"/>
+      <c r="A19" s="187"/>
       <c r="B19" s="94" t="s">
         <v>61</v>
       </c>
@@ -9393,7 +9578,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="125"/>
+      <c r="A20" s="188"/>
       <c r="B20" s="94" t="s">
         <v>63</v>
       </c>
@@ -9485,15 +9670,15 @@
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="141" t="s">
+      <c r="I3" s="215" t="s">
         <v>133</v>
       </c>
-      <c r="J3" s="134"/>
+      <c r="J3" s="212"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="142" t="s">
+      <c r="L3" s="216" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="134"/>
+      <c r="M3" s="212"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -9600,7 +9785,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="214" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="94" t="s">
@@ -9630,12 +9815,12 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="124"/>
+      <c r="A9" s="187"/>
       <c r="B9" s="94" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="116"/>
-      <c r="D9" s="137"/>
+      <c r="D9" s="217"/>
       <c r="E9" s="1"/>
       <c r="F9" s="38" t="s">
         <v>28</v>
@@ -9656,14 +9841,14 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="125"/>
+      <c r="A10" s="188"/>
       <c r="B10" s="94" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="55">
         <v>5988</v>
       </c>
-      <c r="D10" s="138"/>
+      <c r="D10" s="218"/>
       <c r="E10" s="1"/>
       <c r="F10" s="38" t="s">
         <v>31</v>
@@ -9690,7 +9875,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="116"/>
-      <c r="D11" s="138"/>
+      <c r="D11" s="218"/>
       <c r="E11" s="1"/>
       <c r="F11" s="61" t="s">
         <v>34</v>
@@ -9711,8 +9896,8 @@
         <v>37</v>
       </c>
       <c r="C12" s="116"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="139" t="s">
+      <c r="D12" s="217"/>
+      <c r="E12" s="219" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="39"/>
@@ -9734,8 +9919,8 @@
         <v>42</v>
       </c>
       <c r="C13" s="116"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="124"/>
+      <c r="D13" s="218"/>
+      <c r="E13" s="187"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
       <c r="I13" s="119"/>
@@ -9750,8 +9935,8 @@
         <v>45</v>
       </c>
       <c r="C14" s="116"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="125"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="188"/>
       <c r="F14" s="39"/>
       <c r="G14" s="40"/>
       <c r="I14" s="119"/>
@@ -9834,7 +10019,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="140" t="s">
+      <c r="A18" s="220" t="s">
         <v>57</v>
       </c>
       <c r="B18" s="94" t="s">
@@ -9860,7 +10045,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="124"/>
+      <c r="A19" s="187"/>
       <c r="B19" s="94" t="s">
         <v>61</v>
       </c>
@@ -9880,7 +10065,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="125"/>
+      <c r="A20" s="188"/>
       <c r="B20" s="94" t="s">
         <v>63</v>
       </c>
@@ -12892,14 +13077,289 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A18:A20"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E14"/>
-    <mergeCell ref="A18:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57AEF1D1-1C2A-43B4-A8A6-446CB590A6DB}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.08984375" style="123" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.08984375" style="123" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="126" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="226" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="229" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="229" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="230" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="224" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="231">
+        <v>95053</v>
+      </c>
+      <c r="C2" s="231">
+        <v>340113</v>
+      </c>
+      <c r="D2" s="232">
+        <f>SUM(B2:C2)</f>
+        <v>435166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="228" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A3" s="224" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="231">
+        <v>116294</v>
+      </c>
+      <c r="C3" s="231">
+        <v>341064</v>
+      </c>
+      <c r="D3" s="232">
+        <f t="shared" ref="D3:D8" si="0">SUM(B3:C3)</f>
+        <v>457358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="224" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="231">
+        <v>178497.2</v>
+      </c>
+      <c r="C4" s="231">
+        <v>785560</v>
+      </c>
+      <c r="D4" s="232">
+        <f t="shared" si="0"/>
+        <v>964057.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="224" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="233">
+        <v>143466</v>
+      </c>
+      <c r="C5" s="225">
+        <v>832770</v>
+      </c>
+      <c r="D5" s="232">
+        <f t="shared" si="0"/>
+        <v>976236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="224" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="231">
+        <v>181591.79</v>
+      </c>
+      <c r="C6" s="169">
+        <v>676076</v>
+      </c>
+      <c r="D6" s="232">
+        <f t="shared" si="0"/>
+        <v>857667.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="224" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="233">
+        <v>73307.91</v>
+      </c>
+      <c r="C7" s="225">
+        <v>767204</v>
+      </c>
+      <c r="D7" s="232">
+        <f t="shared" si="0"/>
+        <v>840511.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="224" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="233">
+        <v>23927.02</v>
+      </c>
+      <c r="C8" s="237">
+        <v>905247</v>
+      </c>
+      <c r="D8" s="232">
+        <f t="shared" si="0"/>
+        <v>929174.02</v>
+      </c>
+      <c r="E8" s="221"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="238"/>
+      <c r="B9" s="239"/>
+      <c r="C9" s="240"/>
+      <c r="D9" s="241"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="238"/>
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="158"/>
+    </row>
+    <row r="11" spans="1:9" ht="14" x14ac:dyDescent="0.3">
+      <c r="A11" s="234" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="234" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="234" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="158"/>
+    </row>
+    <row r="12" spans="1:9" ht="14" x14ac:dyDescent="0.3">
+      <c r="A12" s="235"/>
+      <c r="B12" s="235"/>
+      <c r="C12" s="234" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="158"/>
+    </row>
+    <row r="13" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="223" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="223" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="242">
+        <v>4</v>
+      </c>
+      <c r="D13" s="158"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="223" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="223" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="232">
+        <v>7</v>
+      </c>
+      <c r="D14" s="158"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="223" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="223" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="232">
+        <v>2</v>
+      </c>
+      <c r="I15" s="227" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="223" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="223" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="223" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="223" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="232">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="223" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="223" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="232">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="223" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="223" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="232">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="223" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="223" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="232">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="236" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" s="222">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="41" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
 </file>